--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_02-09-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_02-09-2025.xlsx
@@ -3569,7 +3569,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>£1424.0</t>
+          <t>£1280.0</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>£1504.0</t>
+          <t>£1360.0</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
